--- a/BackEnd/dimensao_Champions_completo.xlsx
+++ b/BackEnd/dimensao_Champions_completo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,53 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I280"/>
+  <dimension ref="A1:K280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Match_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Rodada_Fase</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ID_Casa</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Time_Casa</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Gols_Casa</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Penaltis_Casa</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Gols_Fora</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Penaltis_Fora</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ID_Fora</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time_Fora</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ID_Fora</t>
         </is>
       </c>
     </row>
@@ -500,16 +498,18 @@
       <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
-      </c>
-      <c r="I2" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -537,16 +537,18 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I3" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -574,16 +576,18 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="5">
@@ -611,16 +615,18 @@
       <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>42</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I5" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -648,16 +654,18 @@
       <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>2836</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="7">
@@ -685,16 +693,18 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="8">
@@ -722,16 +732,18 @@
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>2681</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Bayer 04 Leverkusen</t>
         </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2681</v>
       </c>
     </row>
     <row r="9">
@@ -759,16 +771,18 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>44</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -796,16 +810,18 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="11">
@@ -833,16 +849,18 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="12">
@@ -870,16 +888,18 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="13">
@@ -907,16 +927,18 @@
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="14">
@@ -938,22 +960,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="15">
@@ -981,16 +1009,18 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="16">
@@ -1018,16 +1048,18 @@
       <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="17">
@@ -1055,16 +1087,18 @@
       <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="18">
@@ -1090,18 +1124,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="19">
@@ -1129,16 +1169,18 @@
       <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="20">
@@ -1166,16 +1208,18 @@
       <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="21">
@@ -1203,16 +1247,18 @@
       <c r="F21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>40</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I21" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1240,16 +1286,18 @@
       <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="23">
@@ -1277,16 +1325,18 @@
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="24">
@@ -1314,16 +1364,18 @@
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="25">
@@ -1351,16 +1403,18 @@
       <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="26">
@@ -1388,16 +1442,18 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>42</v>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I26" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="27">
@@ -1425,16 +1481,18 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="28">
@@ -1462,16 +1520,18 @@
       <c r="F28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>3</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="29">
@@ -1499,16 +1559,18 @@
       <c r="F29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="30">
@@ -1536,16 +1598,18 @@
       <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>42</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I30" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -1573,16 +1637,18 @@
       <c r="F31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I31" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="32">
@@ -1610,16 +1676,18 @@
       <c r="F32" t="n">
         <v>1</v>
       </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>2685</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2685</v>
       </c>
     </row>
     <row r="33">
@@ -1647,16 +1715,18 @@
       <c r="F33" t="n">
         <v>4</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>2352</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2352</v>
       </c>
     </row>
     <row r="34">
@@ -1684,16 +1754,18 @@
       <c r="F34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I34" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="35">
@@ -1721,16 +1793,18 @@
       <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
-      </c>
-      <c r="I35" t="n">
-        <v>3313</v>
       </c>
     </row>
     <row r="36">
@@ -1758,16 +1832,18 @@
       <c r="F36" t="n">
         <v>1</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>2836</v>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="37">
@@ -1795,16 +1871,18 @@
       <c r="F37" t="n">
         <v>3</v>
       </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>AS Monaco</t>
         </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1653</v>
       </c>
     </row>
     <row r="38">
@@ -1832,16 +1910,18 @@
       <c r="F38" t="n">
         <v>2</v>
       </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
         <v>2692</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1869,16 +1949,18 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I39" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="40">
@@ -1906,16 +1988,18 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I40" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="41">
@@ -1943,16 +2027,18 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="42">
@@ -1980,16 +2066,18 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>42</v>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I42" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -2017,16 +2105,18 @@
       <c r="F43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
         <v>2</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
         <v>44</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2054,16 +2144,18 @@
       <c r="F44" t="n">
         <v>3</v>
       </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I44" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="45">
@@ -2091,16 +2183,18 @@
       <c r="F45" t="n">
         <v>2</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>2686</v>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
-      </c>
-      <c r="I45" t="n">
-        <v>2686</v>
       </c>
     </row>
     <row r="46">
@@ -2128,16 +2222,18 @@
       <c r="F46" t="n">
         <v>0</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
         <v>3</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I46" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="47">
@@ -2165,16 +2261,18 @@
       <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
         <v>3</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I47" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="48">
@@ -2202,16 +2300,18 @@
       <c r="F48" t="n">
         <v>0</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
         <v>3</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I48" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="49">
@@ -2239,16 +2339,18 @@
       <c r="F49" t="n">
         <v>2</v>
       </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I49" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="50">
@@ -2276,16 +2378,18 @@
       <c r="F50" t="n">
         <v>2</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
         <v>3</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I50" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="51">
@@ -2313,16 +2417,18 @@
       <c r="F51" t="n">
         <v>2</v>
       </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>2686</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
-      </c>
-      <c r="I51" t="n">
-        <v>2686</v>
       </c>
     </row>
     <row r="52">
@@ -2350,16 +2456,18 @@
       <c r="F52" t="n">
         <v>0</v>
       </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I52" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="53">
@@ -2387,16 +2495,18 @@
       <c r="F53" t="n">
         <v>1</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
         <v>2692</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -2424,16 +2534,18 @@
       <c r="F54" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="n">
         <v>2</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I54" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="55">
@@ -2455,22 +2567,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I55" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="56">
@@ -2498,16 +2612,18 @@
       <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
         <v>3</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I56" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="57">
@@ -2535,16 +2651,18 @@
       <c r="F57" t="n">
         <v>3</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
         <v>3</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>AS Monaco</t>
         </is>
-      </c>
-      <c r="I57" t="n">
-        <v>1653</v>
       </c>
     </row>
     <row r="58">
@@ -2572,16 +2690,18 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>2352</v>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
-      </c>
-      <c r="I58" t="n">
-        <v>2352</v>
       </c>
     </row>
     <row r="59">
@@ -2609,16 +2729,18 @@
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>3001</v>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
-      </c>
-      <c r="I59" t="n">
-        <v>3001</v>
       </c>
     </row>
     <row r="60">
@@ -2646,16 +2768,18 @@
       <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="G60" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>2687</v>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
-      </c>
-      <c r="I60" t="n">
-        <v>2687</v>
       </c>
     </row>
     <row r="61">
@@ -2683,16 +2807,18 @@
       <c r="F61" t="n">
         <v>7</v>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Stade Brestois</t>
         </is>
-      </c>
-      <c r="I61" t="n">
-        <v>1715</v>
       </c>
     </row>
     <row r="62">
@@ -2720,16 +2846,18 @@
       <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
         <v>2</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>2051</v>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>SK Sturm Graz</t>
         </is>
-      </c>
-      <c r="I62" t="n">
-        <v>2051</v>
       </c>
     </row>
     <row r="63">
@@ -2757,16 +2885,18 @@
       <c r="F63" t="n">
         <v>3</v>
       </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I63" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="64">
@@ -2794,16 +2924,18 @@
       <c r="F64" t="n">
         <v>5</v>
       </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>2445</v>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>BSC Young Boys</t>
         </is>
-      </c>
-      <c r="I64" t="n">
-        <v>2445</v>
       </c>
     </row>
     <row r="65">
@@ -2831,16 +2963,18 @@
       <c r="F65" t="n">
         <v>4</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I65" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="66">
@@ -2868,16 +3002,18 @@
       <c r="F66" t="n">
         <v>0</v>
       </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="n">
+        <v>2685</v>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
-      </c>
-      <c r="I66" t="n">
-        <v>2685</v>
       </c>
     </row>
     <row r="67">
@@ -2899,22 +3035,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="n">
+        <v>5149</v>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>FK Crvena zvezda</t>
         </is>
-      </c>
-      <c r="I67" t="n">
-        <v>5149</v>
       </c>
     </row>
     <row r="68">
@@ -2942,16 +3080,18 @@
       <c r="F68" t="n">
         <v>3</v>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>AS Monaco</t>
         </is>
-      </c>
-      <c r="I68" t="n">
-        <v>1653</v>
       </c>
     </row>
     <row r="69">
@@ -2979,16 +3119,18 @@
       <c r="F69" t="n">
         <v>2</v>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>17</v>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
-      </c>
-      <c r="I69" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="70">
@@ -3016,16 +3158,18 @@
       <c r="F70" t="n">
         <v>2</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
         <v>3</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I70" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="71">
@@ -3053,16 +3197,18 @@
       <c r="F71" t="n">
         <v>5</v>
       </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="n">
+        <v>2051</v>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>SK Sturm Graz</t>
         </is>
-      </c>
-      <c r="I71" t="n">
-        <v>2051</v>
       </c>
     </row>
     <row r="72">
@@ -3090,16 +3236,18 @@
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="n">
+        <v>40</v>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I72" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -3127,16 +3275,18 @@
       <c r="F73" t="n">
         <v>1</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
         <v>3</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="n">
+        <v>2677</v>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>VfB Stuttgart</t>
         </is>
-      </c>
-      <c r="I73" t="n">
-        <v>2677</v>
       </c>
     </row>
     <row r="74">
@@ -3164,16 +3314,18 @@
       <c r="F74" t="n">
         <v>2</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="n">
         <v>3</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I74" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="75">
@@ -3201,16 +3353,18 @@
       <c r="F75" t="n">
         <v>2</v>
       </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I75" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="76">
@@ -3238,16 +3392,18 @@
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="n">
+        <v>2687</v>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
-      </c>
-      <c r="I76" t="n">
-        <v>2687</v>
       </c>
     </row>
     <row r="77">
@@ -3275,16 +3431,18 @@
       <c r="F77" t="n">
         <v>2</v>
       </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="n">
+        <v>2681</v>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Bayer 04 Leverkusen</t>
         </is>
-      </c>
-      <c r="I77" t="n">
-        <v>2681</v>
       </c>
     </row>
     <row r="78">
@@ -3306,22 +3464,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>2</v>
       </c>
-      <c r="G78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I78" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="79">
@@ -3349,16 +3509,18 @@
       <c r="F79" t="n">
         <v>4</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
         <v>5</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I79" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="80">
@@ -3386,16 +3548,18 @@
       <c r="F80" t="n">
         <v>2</v>
       </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>Stade Brestois</t>
         </is>
-      </c>
-      <c r="I80" t="n">
-        <v>1715</v>
       </c>
     </row>
     <row r="81">
@@ -3423,16 +3587,18 @@
       <c r="F81" t="n">
         <v>2</v>
       </c>
-      <c r="G81" t="n">
-        <v>1</v>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="n">
+        <v>3001</v>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
-      </c>
-      <c r="I81" t="n">
-        <v>3001</v>
       </c>
     </row>
     <row r="82">
@@ -3460,16 +3626,18 @@
       <c r="F82" t="n">
         <v>1</v>
       </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="n">
+        <v>2445</v>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>BSC Young Boys</t>
         </is>
-      </c>
-      <c r="I82" t="n">
-        <v>2445</v>
       </c>
     </row>
     <row r="83">
@@ -3497,16 +3665,18 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I83" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="84">
@@ -3528,22 +3698,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="n">
+        <v>24264</v>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>Girona FC</t>
         </is>
-      </c>
-      <c r="I84" t="n">
-        <v>24264</v>
       </c>
     </row>
     <row r="85">
@@ -3571,16 +3743,18 @@
       <c r="F85" t="n">
         <v>3</v>
       </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I85" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="86">
@@ -3608,16 +3782,18 @@
       <c r="F86" t="n">
         <v>3</v>
       </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="n">
+        <v>2032</v>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>GNK Dinamo Zagreb</t>
         </is>
-      </c>
-      <c r="I86" t="n">
-        <v>2032</v>
       </c>
     </row>
     <row r="87">
@@ -3645,16 +3821,18 @@
       <c r="F87" t="n">
         <v>4</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
         <v>2</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="n">
+        <v>17</v>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
-      </c>
-      <c r="I87" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="88">
@@ -3682,16 +3860,18 @@
       <c r="F88" t="n">
         <v>5</v>
       </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I88" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="89">
@@ -3719,16 +3899,18 @@
       <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>5149</v>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>FK Crvena zvezda</t>
         </is>
-      </c>
-      <c r="I89" t="n">
-        <v>5149</v>
       </c>
     </row>
     <row r="90">
@@ -3756,16 +3938,18 @@
       <c r="F90" t="n">
         <v>6</v>
       </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="inlineStr">
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I90" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="91">
@@ -3793,16 +3977,18 @@
       <c r="F91" t="n">
         <v>1</v>
       </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>36360</v>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
-      </c>
-      <c r="I91" t="n">
-        <v>36360</v>
       </c>
     </row>
     <row r="92">
@@ -3830,16 +4016,18 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="inlineStr">
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I92" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="93">
@@ -3867,16 +4055,18 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="inlineStr">
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="n">
+        <v>42</v>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I93" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="94">
@@ -3904,16 +4094,18 @@
       <c r="F94" t="n">
         <v>2</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
         <v>5</v>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I94" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="95">
@@ -3941,16 +4133,18 @@
       <c r="F95" t="n">
         <v>0</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
         <v>6</v>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="n">
+        <v>2836</v>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
-      </c>
-      <c r="I95" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="96">
@@ -3978,16 +4172,18 @@
       <c r="F96" t="n">
         <v>2</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
         <v>3</v>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="n">
         <v>2692</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -4015,16 +4211,18 @@
       <c r="F97" t="n">
         <v>1</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
         <v>6</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="n">
+        <v>2686</v>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
-      </c>
-      <c r="I97" t="n">
-        <v>2686</v>
       </c>
     </row>
     <row r="98">
@@ -4052,16 +4250,18 @@
       <c r="F98" t="n">
         <v>5</v>
       </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I98" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="99">
@@ -4089,16 +4289,18 @@
       <c r="F99" t="n">
         <v>1</v>
       </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="n">
+        <v>36360</v>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
-      </c>
-      <c r="I99" t="n">
-        <v>36360</v>
       </c>
     </row>
     <row r="100">
@@ -4126,16 +4328,18 @@
       <c r="F100" t="n">
         <v>1</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
         <v>5</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="n">
+        <v>42</v>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I100" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="101">
@@ -4163,16 +4367,18 @@
       <c r="F101" t="n">
         <v>1</v>
       </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I101" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="102">
@@ -4200,16 +4406,18 @@
       <c r="F102" t="n">
         <v>3</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
         <v>3</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I102" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="103">
@@ -4237,16 +4445,18 @@
       <c r="F103" t="n">
         <v>3</v>
       </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>Stade Brestois</t>
         </is>
-      </c>
-      <c r="I103" t="n">
-        <v>1715</v>
       </c>
     </row>
     <row r="104">
@@ -4274,16 +4484,18 @@
       <c r="F104" t="n">
         <v>5</v>
       </c>
-      <c r="G104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="n">
+        <v>2677</v>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>VfB Stuttgart</t>
         </is>
-      </c>
-      <c r="I104" t="n">
-        <v>2677</v>
       </c>
     </row>
     <row r="105">
@@ -4311,16 +4523,18 @@
       <c r="F105" t="n">
         <v>1</v>
       </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="n">
+        <v>24264</v>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>Girona FC</t>
         </is>
-      </c>
-      <c r="I105" t="n">
-        <v>24264</v>
       </c>
     </row>
     <row r="106">
@@ -4348,16 +4562,18 @@
       <c r="F106" t="n">
         <v>1</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="n">
         <v>2</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I106" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="107">
@@ -4385,16 +4601,18 @@
       <c r="F107" t="n">
         <v>1</v>
       </c>
-      <c r="G107" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" t="inlineStr">
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I107" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="108">
@@ -4422,16 +4640,18 @@
       <c r="F108" t="n">
         <v>3</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
         <v>2</v>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
-      </c>
-      <c r="I108" t="n">
-        <v>3313</v>
       </c>
     </row>
     <row r="109">
@@ -4459,16 +4679,18 @@
       <c r="F109" t="n">
         <v>2</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
         <v>3</v>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I109" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="110">
@@ -4496,16 +4718,18 @@
       <c r="F110" t="n">
         <v>0</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
         <v>3</v>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I110" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="111">
@@ -4533,16 +4757,18 @@
       <c r="F111" t="n">
         <v>0</v>
       </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>2687</v>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
-      </c>
-      <c r="I111" t="n">
-        <v>2687</v>
       </c>
     </row>
     <row r="112">
@@ -4564,22 +4790,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="F112" t="n">
         <v>2</v>
       </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I112" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="113">
@@ -4607,16 +4835,18 @@
       <c r="F113" t="n">
         <v>0</v>
       </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" t="inlineStr">
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="n">
+        <v>2352</v>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
-      </c>
-      <c r="I113" t="n">
-        <v>2352</v>
       </c>
     </row>
     <row r="114">
@@ -4644,16 +4874,18 @@
       <c r="F114" t="n">
         <v>0</v>
       </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="I114" t="n">
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="n">
         <v>44</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -4681,16 +4913,18 @@
       <c r="F115" t="n">
         <v>1</v>
       </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="inlineStr">
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I115" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="116">
@@ -4718,16 +4952,18 @@
       <c r="F116" t="n">
         <v>2</v>
       </c>
-      <c r="G116" t="n">
-        <v>1</v>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="n">
+        <v>3001</v>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
-      </c>
-      <c r="I116" t="n">
-        <v>3001</v>
       </c>
     </row>
     <row r="117">
@@ -4755,16 +4991,18 @@
       <c r="F117" t="n">
         <v>2</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="n">
         <v>3</v>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="n">
+        <v>40</v>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I117" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="118">
@@ -4792,16 +5030,18 @@
       <c r="F118" t="n">
         <v>0</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="n">
         <v>3</v>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I118" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="119">
@@ -4829,16 +5069,18 @@
       <c r="F119" t="n">
         <v>1</v>
       </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="inlineStr">
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I119" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="120">
@@ -4866,16 +5108,18 @@
       <c r="F120" t="n">
         <v>1</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="n">
         <v>5</v>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I120" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="121">
@@ -4903,16 +5147,18 @@
       <c r="F121" t="n">
         <v>2</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
         <v>3</v>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I121" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="122">
@@ -4940,16 +5186,18 @@
       <c r="F122" t="n">
         <v>0</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="n">
         <v>2</v>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>3001</v>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
-      </c>
-      <c r="I122" t="n">
-        <v>3001</v>
       </c>
     </row>
     <row r="123">
@@ -4977,16 +5225,18 @@
       <c r="F123" t="n">
         <v>2</v>
       </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="inlineStr">
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="n">
+        <v>2685</v>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
-      </c>
-      <c r="I123" t="n">
-        <v>2685</v>
       </c>
     </row>
     <row r="124">
@@ -5014,16 +5264,18 @@
       <c r="F124" t="n">
         <v>0</v>
       </c>
-      <c r="G124" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" t="inlineStr">
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="n">
+        <v>2677</v>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>VfB Stuttgart</t>
         </is>
-      </c>
-      <c r="I124" t="n">
-        <v>2677</v>
       </c>
     </row>
     <row r="125">
@@ -5051,16 +5303,18 @@
       <c r="F125" t="n">
         <v>1</v>
       </c>
-      <c r="G125" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" t="inlineStr">
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I125" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="126">
@@ -5088,16 +5342,18 @@
       <c r="F126" t="n">
         <v>1</v>
       </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="inlineStr">
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
-      </c>
-      <c r="I126" t="n">
-        <v>3313</v>
       </c>
     </row>
     <row r="127">
@@ -5125,16 +5381,18 @@
       <c r="F127" t="n">
         <v>5</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
         <v>2</v>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I127" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="128">
@@ -5162,16 +5420,18 @@
       <c r="F128" t="n">
         <v>0</v>
       </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="inlineStr">
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="n">
+        <v>2352</v>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
-      </c>
-      <c r="I128" t="n">
-        <v>2352</v>
       </c>
     </row>
     <row r="129">
@@ -5199,16 +5459,18 @@
       <c r="F129" t="n">
         <v>1</v>
       </c>
-      <c r="G129" t="n">
-        <v>1</v>
-      </c>
-      <c r="H129" t="inlineStr">
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="n">
+        <v>2681</v>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>Bayer 04 Leverkusen</t>
         </is>
-      </c>
-      <c r="I129" t="n">
-        <v>2681</v>
       </c>
     </row>
     <row r="130">
@@ -5236,16 +5498,18 @@
       <c r="F130" t="n">
         <v>0</v>
       </c>
-      <c r="G130" t="n">
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
         <v>2</v>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="n">
+        <v>2032</v>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>GNK Dinamo Zagreb</t>
         </is>
-      </c>
-      <c r="I130" t="n">
-        <v>2032</v>
       </c>
     </row>
     <row r="131">
@@ -5273,16 +5537,18 @@
       <c r="F131" t="n">
         <v>1</v>
       </c>
-      <c r="G131" t="n">
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
         <v>3</v>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I131" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="132">
@@ -5310,16 +5576,18 @@
       <c r="F132" t="n">
         <v>1</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
         <v>3</v>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I132" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="133">
@@ -5347,16 +5615,18 @@
       <c r="F133" t="n">
         <v>0</v>
       </c>
-      <c r="G133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H133" t="inlineStr">
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I133" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="134">
@@ -5384,16 +5654,18 @@
       <c r="F134" t="n">
         <v>0</v>
       </c>
-      <c r="G134" t="n">
-        <v>1</v>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="I134" t="n">
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="n">
         <v>44</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -5421,16 +5693,18 @@
       <c r="F135" t="n">
         <v>5</v>
       </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="inlineStr">
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I135" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="136">
@@ -5458,16 +5732,18 @@
       <c r="F136" t="n">
         <v>4</v>
       </c>
-      <c r="G136" t="n">
-        <v>1</v>
-      </c>
-      <c r="H136" t="inlineStr">
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I136" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="137">
@@ -5495,16 +5771,18 @@
       <c r="F137" t="n">
         <v>1</v>
       </c>
-      <c r="G137" t="n">
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
         <v>4</v>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="n">
+        <v>2032</v>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>GNK Dinamo Zagreb</t>
         </is>
-      </c>
-      <c r="I137" t="n">
-        <v>2032</v>
       </c>
     </row>
     <row r="138">
@@ -5532,16 +5810,18 @@
       <c r="F138" t="n">
         <v>4</v>
       </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="inlineStr">
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="n">
+        <v>24264</v>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>Girona FC</t>
         </is>
-      </c>
-      <c r="I138" t="n">
-        <v>24264</v>
       </c>
     </row>
     <row r="139">
@@ -5569,16 +5849,18 @@
       <c r="F139" t="n">
         <v>0</v>
       </c>
-      <c r="G139" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>AS Monaco</t>
         </is>
-      </c>
-      <c r="I139" t="n">
-        <v>1653</v>
       </c>
     </row>
     <row r="140">
@@ -5606,16 +5888,18 @@
       <c r="F140" t="n">
         <v>3</v>
       </c>
-      <c r="G140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" t="inlineStr">
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
+        <v>36360</v>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
-      </c>
-      <c r="I140" t="n">
-        <v>36360</v>
       </c>
     </row>
     <row r="141">
@@ -5643,16 +5927,18 @@
       <c r="F141" t="n">
         <v>1</v>
       </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="inlineStr">
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>2051</v>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>SK Sturm Graz</t>
         </is>
-      </c>
-      <c r="I141" t="n">
-        <v>2051</v>
       </c>
     </row>
     <row r="142">
@@ -5680,16 +5966,18 @@
       <c r="F142" t="n">
         <v>1</v>
       </c>
-      <c r="G142" t="n">
-        <v>1</v>
-      </c>
-      <c r="H142" t="inlineStr">
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
+        <v>2687</v>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
-      </c>
-      <c r="I142" t="n">
-        <v>2687</v>
       </c>
     </row>
     <row r="143">
@@ -5711,22 +5999,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="F143" t="n">
         <v>4</v>
       </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="inlineStr">
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>2681</v>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>Bayer 04 Leverkusen</t>
         </is>
-      </c>
-      <c r="I143" t="n">
-        <v>2681</v>
       </c>
     </row>
     <row r="144">
@@ -5754,16 +6044,18 @@
       <c r="F144" t="n">
         <v>4</v>
       </c>
-      <c r="G144" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" t="inlineStr">
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>17</v>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
-      </c>
-      <c r="I144" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="145">
@@ -5791,16 +6083,18 @@
       <c r="F145" t="n">
         <v>1</v>
       </c>
-      <c r="G145" t="n">
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
         <v>3</v>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="I145" t="n">
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
         <v>2692</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -5828,16 +6122,18 @@
       <c r="F146" t="n">
         <v>2</v>
       </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="inlineStr">
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>2445</v>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>BSC Young Boys</t>
         </is>
-      </c>
-      <c r="I146" t="n">
-        <v>2445</v>
       </c>
     </row>
     <row r="147">
@@ -5865,16 +6161,18 @@
       <c r="F147" t="n">
         <v>1</v>
       </c>
-      <c r="G147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="inlineStr">
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>40</v>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I147" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -5902,16 +6200,18 @@
       <c r="F148" t="n">
         <v>1</v>
       </c>
-      <c r="G148" t="n">
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
         <v>2</v>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Stade Brestois</t>
         </is>
-      </c>
-      <c r="I148" t="n">
-        <v>1715</v>
       </c>
     </row>
     <row r="149">
@@ -5939,16 +6239,18 @@
       <c r="F149" t="n">
         <v>1</v>
       </c>
-      <c r="G149" t="n">
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="n">
         <v>3</v>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I149" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="150">
@@ -5976,16 +6278,18 @@
       <c r="F150" t="n">
         <v>0</v>
       </c>
-      <c r="G150" t="n">
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="n">
         <v>2</v>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>2686</v>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
-      </c>
-      <c r="I150" t="n">
-        <v>2686</v>
       </c>
     </row>
     <row r="151">
@@ -6013,16 +6317,18 @@
       <c r="F151" t="n">
         <v>1</v>
       </c>
-      <c r="G151" t="n">
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
         <v>2</v>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>2836</v>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
-      </c>
-      <c r="I151" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="152">
@@ -6050,16 +6356,18 @@
       <c r="F152" t="n">
         <v>0</v>
       </c>
-      <c r="G152" t="n">
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="n">
         <v>3</v>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="n">
+        <v>2673</v>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>Borussia Dortmund</t>
         </is>
-      </c>
-      <c r="I152" t="n">
-        <v>2673</v>
       </c>
     </row>
     <row r="153">
@@ -6087,16 +6395,18 @@
       <c r="F153" t="n">
         <v>1</v>
       </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="inlineStr">
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="n">
+        <v>24264</v>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Girona FC</t>
         </is>
-      </c>
-      <c r="I153" t="n">
-        <v>24264</v>
       </c>
     </row>
     <row r="154">
@@ -6124,16 +6434,18 @@
       <c r="F154" t="n">
         <v>0</v>
       </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="inlineStr">
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="n">
+        <v>2697</v>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>Inter</t>
         </is>
-      </c>
-      <c r="I154" t="n">
-        <v>2697</v>
       </c>
     </row>
     <row r="155">
@@ -6161,16 +6473,18 @@
       <c r="F155" t="n">
         <v>1</v>
       </c>
-      <c r="G155" t="n">
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="n">
         <v>2</v>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="n">
+        <v>3006</v>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>Benfica</t>
         </is>
-      </c>
-      <c r="I155" t="n">
-        <v>3006</v>
       </c>
     </row>
     <row r="156">
@@ -6198,16 +6512,18 @@
       <c r="F156" t="n">
         <v>0</v>
       </c>
-      <c r="G156" t="n">
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
         <v>4</v>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="n">
+        <v>2681</v>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>Bayer 04 Leverkusen</t>
         </is>
-      </c>
-      <c r="I156" t="n">
-        <v>2681</v>
       </c>
     </row>
     <row r="157">
@@ -6235,16 +6551,18 @@
       <c r="F157" t="n">
         <v>2</v>
       </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="inlineStr">
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="n">
+        <v>2051</v>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>SK Sturm Graz</t>
         </is>
-      </c>
-      <c r="I157" t="n">
-        <v>2051</v>
       </c>
     </row>
     <row r="158">
@@ -6272,16 +6590,18 @@
       <c r="F158" t="n">
         <v>2</v>
       </c>
-      <c r="G158" t="n">
-        <v>1</v>
-      </c>
-      <c r="H158" t="inlineStr">
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="n">
+        <v>36360</v>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
-      </c>
-      <c r="I158" t="n">
-        <v>36360</v>
       </c>
     </row>
     <row r="159">
@@ -6309,16 +6629,18 @@
       <c r="F159" t="n">
         <v>0</v>
       </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" t="inlineStr">
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="n">
+        <v>42</v>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>Arsenal</t>
         </is>
-      </c>
-      <c r="I159" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="160">
@@ -6346,16 +6668,18 @@
       <c r="F160" t="n">
         <v>2</v>
       </c>
-      <c r="G160" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" t="inlineStr">
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="n">
+        <v>2817</v>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>FC Barcelona</t>
         </is>
-      </c>
-      <c r="I160" t="n">
-        <v>2817</v>
       </c>
     </row>
     <row r="161">
@@ -6383,16 +6707,18 @@
       <c r="F161" t="n">
         <v>0</v>
       </c>
-      <c r="G161" t="n">
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="n">
         <v>4</v>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>Stade Brestois</t>
         </is>
-      </c>
-      <c r="I161" t="n">
-        <v>1715</v>
       </c>
     </row>
     <row r="162">
@@ -6420,16 +6746,18 @@
       <c r="F162" t="n">
         <v>1</v>
       </c>
-      <c r="G162" t="n">
-        <v>1</v>
-      </c>
-      <c r="H162" t="inlineStr">
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I162" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="163">
@@ -6457,16 +6785,18 @@
       <c r="F163" t="n">
         <v>1</v>
       </c>
-      <c r="G163" t="n">
-        <v>1</v>
-      </c>
-      <c r="H163" t="inlineStr">
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="n">
+        <v>3001</v>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>Sporting CP</t>
         </is>
-      </c>
-      <c r="I163" t="n">
-        <v>3001</v>
       </c>
     </row>
     <row r="164">
@@ -6494,16 +6824,18 @@
       <c r="F164" t="n">
         <v>7</v>
       </c>
-      <c r="G164" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" t="inlineStr">
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="n">
+        <v>2352</v>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>Celtic</t>
         </is>
-      </c>
-      <c r="I164" t="n">
-        <v>2352</v>
       </c>
     </row>
     <row r="165">
@@ -6531,16 +6863,18 @@
       <c r="F165" t="n">
         <v>4</v>
       </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="inlineStr">
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="n">
+        <v>5149</v>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>FK Crvena zvezda</t>
         </is>
-      </c>
-      <c r="I165" t="n">
-        <v>5149</v>
       </c>
     </row>
     <row r="166">
@@ -6568,16 +6902,18 @@
       <c r="F166" t="n">
         <v>1</v>
       </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="I166" t="n">
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="n">
         <v>2692</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -6605,16 +6941,18 @@
       <c r="F167" t="n">
         <v>0</v>
       </c>
-      <c r="G167" t="n">
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="n">
         <v>4</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="n">
+        <v>17</v>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>Manchester City</t>
         </is>
-      </c>
-      <c r="I167" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="168">
@@ -6642,16 +6980,18 @@
       <c r="F168" t="n">
         <v>2</v>
       </c>
-      <c r="G168" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" t="inlineStr">
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="n">
+        <v>1644</v>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>Paris Saint-Germain</t>
         </is>
-      </c>
-      <c r="I168" t="n">
-        <v>1644</v>
       </c>
     </row>
     <row r="169">
@@ -6679,16 +7019,18 @@
       <c r="F169" t="n">
         <v>5</v>
       </c>
-      <c r="G169" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" t="inlineStr">
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>2445</v>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>BSC Young Boys</t>
         </is>
-      </c>
-      <c r="I169" t="n">
-        <v>2445</v>
       </c>
     </row>
     <row r="170">
@@ -6716,16 +7058,18 @@
       <c r="F170" t="n">
         <v>0</v>
       </c>
-      <c r="G170" t="n">
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="n">
         <v>3</v>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="n">
+        <v>2686</v>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
-      </c>
-      <c r="I170" t="n">
-        <v>2686</v>
       </c>
     </row>
     <row r="171">
@@ -6753,16 +7097,18 @@
       <c r="F171" t="n">
         <v>2</v>
       </c>
-      <c r="G171" t="n">
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="n">
         <v>3</v>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="n">
+        <v>2959</v>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>Feyenoord</t>
         </is>
-      </c>
-      <c r="I171" t="n">
-        <v>2959</v>
       </c>
     </row>
     <row r="172">
@@ -6790,16 +7136,18 @@
       <c r="F172" t="n">
         <v>0</v>
       </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="inlineStr">
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>1</v>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I172" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="173">
@@ -6827,16 +7175,18 @@
       <c r="F173" t="n">
         <v>2</v>
       </c>
-      <c r="G173" t="n">
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="n">
         <v>2</v>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="n">
+        <v>1653</v>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>AS Monaco</t>
         </is>
-      </c>
-      <c r="I173" t="n">
-        <v>1653</v>
       </c>
     </row>
     <row r="174">
@@ -6864,16 +7214,18 @@
       <c r="F174" t="n">
         <v>4</v>
       </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" t="inlineStr">
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>2836</v>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>Atlético Madrid</t>
         </is>
-      </c>
-      <c r="I174" t="n">
-        <v>2836</v>
       </c>
     </row>
     <row r="175">
@@ -6901,16 +7253,18 @@
       <c r="F175" t="n">
         <v>2</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="n">
         <v>3</v>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="n">
+        <v>2687</v>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>Juventus</t>
         </is>
-      </c>
-      <c r="I175" t="n">
-        <v>2687</v>
       </c>
     </row>
     <row r="176">
@@ -6938,16 +7292,18 @@
       <c r="F176" t="n">
         <v>1</v>
       </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" t="inlineStr">
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="n">
+        <v>2672</v>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>FC Bayern München</t>
         </is>
-      </c>
-      <c r="I176" t="n">
-        <v>2672</v>
       </c>
     </row>
     <row r="177">
@@ -6969,22 +7325,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Liverpool FC</t>
         </is>
       </c>
       <c r="F177" t="n">
         <v>2</v>
       </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" t="inlineStr">
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="n">
+        <v>2685</v>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>Bologna</t>
         </is>
-      </c>
-      <c r="I177" t="n">
-        <v>2685</v>
       </c>
     </row>
     <row r="178">
@@ -7012,16 +7370,18 @@
       <c r="F178" t="n">
         <v>1</v>
       </c>
-      <c r="G178" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" t="inlineStr">
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="n">
+        <v>2829</v>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>Real Madrid</t>
         </is>
-      </c>
-      <c r="I178" t="n">
-        <v>2829</v>
       </c>
     </row>
     <row r="179">
@@ -7049,16 +7409,18 @@
       <c r="F179" t="n">
         <v>5</v>
       </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="inlineStr">
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="n">
+        <v>5149</v>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>FK Crvena zvezda</t>
         </is>
-      </c>
-      <c r="I179" t="n">
-        <v>5149</v>
       </c>
     </row>
     <row r="180">
@@ -7080,22 +7442,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F180" t="n">
         <v>3</v>
       </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="inlineStr">
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="n">
+        <v>2888</v>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
-      </c>
-      <c r="I180" t="n">
-        <v>2888</v>
       </c>
     </row>
     <row r="181">
@@ -7123,16 +7487,18 @@
       <c r="F181" t="n">
         <v>2</v>
       </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" t="inlineStr">
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K181" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I181" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="182">
@@ -7160,16 +7526,18 @@
       <c r="F182" t="n">
         <v>1</v>
       </c>
-      <c r="G182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H182" t="inlineStr">
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I182" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="183">
@@ -7197,16 +7565,18 @@
       <c r="F183" t="n">
         <v>3</v>
       </c>
-      <c r="G183" t="n">
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="n">
         <v>4</v>
       </c>
-      <c r="H183" t="inlineStr">
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="n">
+        <v>1892</v>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>Malmö FF</t>
         </is>
-      </c>
-      <c r="I183" t="n">
-        <v>1892</v>
       </c>
     </row>
     <row r="184">
@@ -7234,16 +7604,18 @@
       <c r="F184" t="n">
         <v>1</v>
       </c>
-      <c r="G184" t="n">
-        <v>1</v>
-      </c>
-      <c r="H184" t="inlineStr">
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="n">
+        <v>1289</v>
+      </c>
+      <c r="K184" t="inlineStr">
         <is>
           <t>FC Midtjylland</t>
         </is>
-      </c>
-      <c r="I184" t="n">
-        <v>1289</v>
       </c>
     </row>
     <row r="185">
@@ -7271,16 +7643,18 @@
       <c r="F185" t="n">
         <v>2</v>
       </c>
-      <c r="G185" t="n">
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="n">
         <v>7</v>
       </c>
-      <c r="H185" t="inlineStr">
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="n">
+        <v>5962</v>
+      </c>
+      <c r="K185" t="inlineStr">
         <is>
           <t>Qarabağ FK</t>
         </is>
-      </c>
-      <c r="I185" t="n">
-        <v>5962</v>
       </c>
     </row>
     <row r="186">
@@ -7308,16 +7682,18 @@
       <c r="F186" t="n">
         <v>2</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="n">
         <v>3</v>
       </c>
-      <c r="H186" t="inlineStr">
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K186" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I186" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="187">
@@ -7345,16 +7721,18 @@
       <c r="F187" t="n">
         <v>0</v>
       </c>
-      <c r="G187" t="n">
-        <v>1</v>
-      </c>
-      <c r="H187" t="inlineStr">
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="n">
+        <v>2216</v>
+      </c>
+      <c r="K187" t="inlineStr">
         <is>
           <t>SK Slavia Praha</t>
         </is>
-      </c>
-      <c r="I187" t="n">
-        <v>2216</v>
       </c>
     </row>
     <row r="188">
@@ -7382,16 +7760,18 @@
       <c r="F188" t="n">
         <v>0</v>
       </c>
-      <c r="G188" t="n">
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="n">
         <v>2</v>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="n">
+        <v>3305</v>
+      </c>
+      <c r="K188" t="inlineStr">
         <is>
           <t>Dynamo Kyiv</t>
         </is>
-      </c>
-      <c r="I188" t="n">
-        <v>3305</v>
       </c>
     </row>
     <row r="189">
@@ -7419,16 +7799,18 @@
       <c r="F189" t="n">
         <v>2</v>
       </c>
-      <c r="G189" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" t="inlineStr">
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="n">
+        <v>2216</v>
+      </c>
+      <c r="K189" t="inlineStr">
         <is>
           <t>SK Slavia Praha</t>
         </is>
-      </c>
-      <c r="I189" t="n">
-        <v>2216</v>
       </c>
     </row>
     <row r="190">
@@ -7456,16 +7838,18 @@
       <c r="F190" t="n">
         <v>2</v>
       </c>
-      <c r="G190" t="n">
-        <v>1</v>
-      </c>
-      <c r="H190" t="inlineStr">
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="n">
+        <v>5149</v>
+      </c>
+      <c r="K190" t="inlineStr">
         <is>
           <t>FK Crvena zvezda</t>
         </is>
-      </c>
-      <c r="I190" t="n">
-        <v>5149</v>
       </c>
     </row>
     <row r="191">
@@ -7493,16 +7877,18 @@
       <c r="F191" t="n">
         <v>3</v>
       </c>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
-      <c r="H191" t="inlineStr">
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="n">
+        <v>5962</v>
+      </c>
+      <c r="K191" t="inlineStr">
         <is>
           <t>Qarabağ FK</t>
         </is>
-      </c>
-      <c r="I191" t="n">
-        <v>5962</v>
       </c>
     </row>
     <row r="192">
@@ -7530,16 +7916,18 @@
       <c r="F192" t="n">
         <v>1</v>
       </c>
-      <c r="G192" t="n">
-        <v>1</v>
-      </c>
-      <c r="H192" t="inlineStr">
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K192" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I192" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="193">
@@ -7567,16 +7955,18 @@
       <c r="F193" t="n">
         <v>0</v>
       </c>
-      <c r="G193" t="n">
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="n">
         <v>2</v>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K193" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I193" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="194">
@@ -7604,16 +7994,18 @@
       <c r="F194" t="n">
         <v>0</v>
       </c>
-      <c r="G194" t="n">
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="n">
         <v>2</v>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K194" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I194" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="195">
@@ -7641,16 +8033,18 @@
       <c r="F195" t="n">
         <v>3</v>
       </c>
-      <c r="G195" t="n">
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="n">
         <v>2</v>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="n">
+        <v>3061</v>
+      </c>
+      <c r="K195" t="inlineStr">
         <is>
           <t>Galatasaray</t>
         </is>
-      </c>
-      <c r="I195" t="n">
-        <v>3061</v>
       </c>
     </row>
     <row r="196">
@@ -7678,16 +8072,18 @@
       <c r="F196" t="n">
         <v>2</v>
       </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="inlineStr">
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="n">
+        <v>1892</v>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>Malmö FF</t>
         </is>
-      </c>
-      <c r="I196" t="n">
-        <v>1892</v>
       </c>
     </row>
     <row r="197">
@@ -7715,16 +8111,18 @@
       <c r="F197" t="n">
         <v>1</v>
       </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="inlineStr">
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="n">
+        <v>3305</v>
+      </c>
+      <c r="K197" t="inlineStr">
         <is>
           <t>Dynamo Kyiv</t>
         </is>
-      </c>
-      <c r="I197" t="n">
-        <v>3305</v>
       </c>
     </row>
     <row r="198">
@@ -7752,16 +8150,18 @@
       <c r="F198" t="n">
         <v>0</v>
       </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="inlineStr">
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="n">
+        <v>1</v>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="n">
+        <v>2445</v>
+      </c>
+      <c r="K198" t="inlineStr">
         <is>
           <t>BSC Young Boys</t>
         </is>
-      </c>
-      <c r="I198" t="n">
-        <v>2445</v>
       </c>
     </row>
     <row r="199">
@@ -7789,16 +8189,18 @@
       <c r="F199" t="n">
         <v>0</v>
       </c>
-      <c r="G199" t="n">
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="n">
         <v>2</v>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="n">
+        <v>2032</v>
+      </c>
+      <c r="K199" t="inlineStr">
         <is>
           <t>GNK Dinamo Zagreb</t>
         </is>
-      </c>
-      <c r="I199" t="n">
-        <v>2032</v>
       </c>
     </row>
     <row r="200">
@@ -7826,16 +8228,18 @@
       <c r="F200" t="n">
         <v>3</v>
       </c>
-      <c r="G200" t="n">
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="n">
         <v>2</v>
       </c>
-      <c r="H200" t="inlineStr">
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="n">
+        <v>1289</v>
+      </c>
+      <c r="K200" t="inlineStr">
         <is>
           <t>FC Midtjylland</t>
         </is>
-      </c>
-      <c r="I200" t="n">
-        <v>1289</v>
       </c>
     </row>
     <row r="201">
@@ -7863,16 +8267,18 @@
       <c r="F201" t="n">
         <v>2</v>
       </c>
-      <c r="G201" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" t="inlineStr">
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="n">
+        <v>1</v>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K201" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I201" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="202">
@@ -7900,16 +8306,18 @@
       <c r="F202" t="n">
         <v>2</v>
       </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-      <c r="H202" t="inlineStr">
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="n">
+        <v>656</v>
+      </c>
+      <c r="K202" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
-      </c>
-      <c r="I202" t="n">
-        <v>656</v>
       </c>
     </row>
     <row r="203">
@@ -7937,16 +8345,18 @@
       <c r="F203" t="n">
         <v>0</v>
       </c>
-      <c r="G203" t="n">
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="n">
         <v>3</v>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="n">
+        <v>40</v>
+      </c>
+      <c r="K203" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
-      </c>
-      <c r="I203" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="204">
@@ -7974,16 +8384,18 @@
       <c r="F204" t="n">
         <v>3</v>
       </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="inlineStr">
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="n">
+        <v>2952</v>
+      </c>
+      <c r="K204" t="inlineStr">
         <is>
           <t>PSV Eindhoven</t>
         </is>
-      </c>
-      <c r="I204" t="n">
-        <v>2952</v>
       </c>
     </row>
     <row r="205">
@@ -8011,16 +8423,18 @@
       <c r="F205" t="n">
         <v>2</v>
       </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-      <c r="H205" t="inlineStr">
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K205" t="inlineStr">
         <is>
           <t>Lille</t>
         </is>
-      </c>
-      <c r="I205" t="n">
-        <v>1643</v>
       </c>
     </row>
     <row r="206">
@@ -8048,16 +8462,18 @@
       <c r="F206" t="n">
         <v>9</v>
       </c>
-      <c r="G206" t="n">
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="n">
         <v>2</v>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="n">
+        <v>2032</v>
+      </c>
+      <c r="K206" t="inlineStr">
         <is>
           <t>GNK Dinamo Zagreb</t>
         </is>
-      </c>
-      <c r="I206" t="n">
-        <v>2032</v>
       </c>
     </row>
     <row r="207">
@@ -8079,22 +8495,24 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F207" t="n">
         <v>1</v>
       </c>
-      <c r="G207" t="n">
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="n">
         <v>3</v>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="n">
         <v>44</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Liverpool FC</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -8122,16 +8540,18 @@
       <c r="F208" t="n">
         <v>3</v>
       </c>
-      <c r="G208" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" t="inlineStr">
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="n">
+        <v>2677</v>
+      </c>
+      <c r="K208" t="inlineStr">
         <is>
           <t>VfB Stuttgart</t>
         </is>
-      </c>
-      <c r="I208" t="n">
-        <v>2677</v>
       </c>
     </row>
     <row r="209">
@@ -8159,16 +8579,18 @@
       <c r="F209" t="n">
         <v>3</v>
       </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" t="inlineStr">
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K209" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I209" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="210">
@@ -8196,16 +8618,18 @@
       <c r="F210" t="n">
         <v>0</v>
       </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="inlineStr">
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="n">
+        <v>3313</v>
+      </c>
+      <c r="K210" t="inlineStr">
         <is>
           <t>Shakhtar Donetsk</t>
         </is>
-      </c>
-      <c r="I210" t="n">
-        <v>3313</v>
       </c>
     </row>
     <row r="211">
@@ -8233,16 +8657,18 @@
       <c r="F211" t="n">
         <v>5</v>
       </c>
-      <c r="G211" t="n">
-        <v>1</v>
-      </c>
-      <c r="H211" t="inlineStr">
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K211" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I211" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="212">
@@ -8270,16 +8696,18 @@
       <c r="F212" t="n">
         <v>3</v>
       </c>
-      <c r="G212" t="n">
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="n">
         <v>2</v>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="n">
+        <v>5235</v>
+      </c>
+      <c r="K212" t="inlineStr">
         <is>
           <t>FK Borac Banja Luka</t>
         </is>
-      </c>
-      <c r="I212" t="n">
-        <v>5235</v>
       </c>
     </row>
     <row r="213">
@@ -8307,16 +8735,18 @@
       <c r="F213" t="n">
         <v>2</v>
       </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" t="inlineStr">
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="n">
+        <v>3361</v>
+      </c>
+      <c r="K213" t="inlineStr">
         <is>
           <t>Dinamo Minsk</t>
         </is>
-      </c>
-      <c r="I213" t="n">
-        <v>3361</v>
       </c>
     </row>
     <row r="214">
@@ -8344,16 +8774,18 @@
       <c r="F214" t="n">
         <v>1</v>
       </c>
-      <c r="G214" t="n">
-        <v>1</v>
-      </c>
-      <c r="H214" t="inlineStr">
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K214" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I214" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="215">
@@ -8381,16 +8813,18 @@
       <c r="F215" t="n">
         <v>5</v>
       </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" t="inlineStr">
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="n">
+        <v>126304</v>
+      </c>
+      <c r="K215" t="inlineStr">
         <is>
           <t>Lincoln Red Imps</t>
         </is>
-      </c>
-      <c r="I215" t="n">
-        <v>126304</v>
       </c>
     </row>
     <row r="216">
@@ -8418,16 +8852,18 @@
       <c r="F216" t="n">
         <v>1</v>
       </c>
-      <c r="G216" t="n">
-        <v>1</v>
-      </c>
-      <c r="H216" t="inlineStr">
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="n">
+        <v>3398</v>
+      </c>
+      <c r="K216" t="inlineStr">
         <is>
           <t>APOEL Nicosia</t>
         </is>
-      </c>
-      <c r="I216" t="n">
-        <v>3398</v>
       </c>
     </row>
     <row r="217">
@@ -8455,16 +8891,18 @@
       <c r="F217" t="n">
         <v>4</v>
       </c>
-      <c r="G217" t="n">
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="n">
         <v>2</v>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="n">
+        <v>3177</v>
+      </c>
+      <c r="K217" t="inlineStr">
         <is>
           <t>Shamrock Rovers</t>
         </is>
-      </c>
-      <c r="I217" t="n">
-        <v>3177</v>
       </c>
     </row>
     <row r="218">
@@ -8492,16 +8930,18 @@
       <c r="F218" t="n">
         <v>2</v>
       </c>
-      <c r="G218" t="n">
-        <v>1</v>
-      </c>
-      <c r="H218" t="inlineStr">
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="n">
+        <v>2443</v>
+      </c>
+      <c r="K218" t="inlineStr">
         <is>
           <t>FC Lugano</t>
         </is>
-      </c>
-      <c r="I218" t="n">
-        <v>2443</v>
       </c>
     </row>
     <row r="219">
@@ -8529,16 +8969,18 @@
       <c r="F219" t="n">
         <v>1</v>
       </c>
-      <c r="G219" t="n">
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="n">
         <v>2</v>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="n">
+        <v>1925</v>
+      </c>
+      <c r="K219" t="inlineStr">
         <is>
           <t>Ferencváros TC</t>
         </is>
-      </c>
-      <c r="I219" t="n">
-        <v>1925</v>
       </c>
     </row>
     <row r="220">
@@ -8566,16 +9008,18 @@
       <c r="F220" t="n">
         <v>5</v>
       </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" t="inlineStr">
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="n">
+        <v>2413</v>
+      </c>
+      <c r="K220" t="inlineStr">
         <is>
           <t>NK Celje</t>
         </is>
-      </c>
-      <c r="I220" t="n">
-        <v>2413</v>
       </c>
     </row>
     <row r="221">
@@ -8603,16 +9047,18 @@
       <c r="F221" t="n">
         <v>3</v>
       </c>
-      <c r="G221" t="n">
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="n">
         <v>2</v>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="n">
+        <v>1892</v>
+      </c>
+      <c r="K221" t="inlineStr">
         <is>
           <t>Malmö FF</t>
         </is>
-      </c>
-      <c r="I221" t="n">
-        <v>1892</v>
       </c>
     </row>
     <row r="222">
@@ -8640,16 +9086,18 @@
       <c r="F222" t="n">
         <v>1</v>
       </c>
-      <c r="G222" t="n">
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="n">
         <v>3</v>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="n">
+        <v>656</v>
+      </c>
+      <c r="K222" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
-      </c>
-      <c r="I222" t="n">
-        <v>656</v>
       </c>
     </row>
     <row r="223">
@@ -8677,16 +9125,18 @@
       <c r="F223" t="n">
         <v>1</v>
       </c>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
-      <c r="H223" t="inlineStr">
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="n">
+        <v>37949</v>
+      </c>
+      <c r="K223" t="inlineStr">
         <is>
           <t>UE Santa Coloma</t>
         </is>
-      </c>
-      <c r="I223" t="n">
-        <v>37949</v>
       </c>
     </row>
     <row r="224">
@@ -8714,16 +9164,18 @@
       <c r="F224" t="n">
         <v>0</v>
       </c>
-      <c r="G224" t="n">
-        <v>1</v>
-      </c>
-      <c r="H224" t="inlineStr">
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="n">
+        <v>3301</v>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>FCSB</t>
         </is>
-      </c>
-      <c r="I224" t="n">
-        <v>3301</v>
       </c>
     </row>
     <row r="225">
@@ -8751,16 +9203,18 @@
       <c r="F225" t="n">
         <v>0</v>
       </c>
-      <c r="G225" t="n">
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
         <v>3</v>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="n">
+        <v>3305</v>
+      </c>
+      <c r="K225" t="inlineStr">
         <is>
           <t>Dynamo Kyiv</t>
         </is>
-      </c>
-      <c r="I225" t="n">
-        <v>3305</v>
       </c>
     </row>
     <row r="226">
@@ -8788,16 +9242,18 @@
       <c r="F226" t="n">
         <v>3</v>
       </c>
-      <c r="G226" t="n">
-        <v>1</v>
-      </c>
-      <c r="H226" t="inlineStr">
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="n">
+        <v>192763</v>
+      </c>
+      <c r="K226" t="inlineStr">
         <is>
           <t>FK Panevėžys</t>
         </is>
-      </c>
-      <c r="I226" t="n">
-        <v>192763</v>
       </c>
     </row>
     <row r="227">
@@ -8825,16 +9281,18 @@
       <c r="F227" t="n">
         <v>1</v>
       </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-      <c r="H227" t="inlineStr">
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="n">
+        <v>43840</v>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>Ludogorets</t>
         </is>
-      </c>
-      <c r="I227" t="n">
-        <v>43840</v>
       </c>
     </row>
     <row r="228">
@@ -8862,16 +9320,18 @@
       <c r="F228" t="n">
         <v>0</v>
       </c>
-      <c r="G228" t="n">
-        <v>1</v>
-      </c>
-      <c r="H228" t="inlineStr">
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="n">
+        <v>3251</v>
+      </c>
+      <c r="K228" t="inlineStr">
         <is>
           <t>PAOK</t>
         </is>
-      </c>
-      <c r="I228" t="n">
-        <v>3251</v>
       </c>
     </row>
     <row r="229">
@@ -8899,16 +9359,18 @@
       <c r="F229" t="n">
         <v>1</v>
       </c>
-      <c r="G229" t="n">
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="n">
         <v>2</v>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="n">
+        <v>43840</v>
+      </c>
+      <c r="K229" t="inlineStr">
         <is>
           <t>Ludogorets</t>
         </is>
-      </c>
-      <c r="I229" t="n">
-        <v>43840</v>
       </c>
     </row>
     <row r="230">
@@ -8936,16 +9398,18 @@
       <c r="F230" t="n">
         <v>2</v>
       </c>
-      <c r="G230" t="n">
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
         <v>2</v>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="n">
+        <v>3251</v>
+      </c>
+      <c r="K230" t="inlineStr">
         <is>
           <t>PAOK</t>
         </is>
-      </c>
-      <c r="I230" t="n">
-        <v>3251</v>
       </c>
     </row>
     <row r="231">
@@ -8973,16 +9437,18 @@
       <c r="F231" t="n">
         <v>2</v>
       </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
-      <c r="H231" t="inlineStr">
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="n">
+        <v>1925</v>
+      </c>
+      <c r="K231" t="inlineStr">
         <is>
           <t>Ferencváros TC</t>
         </is>
-      </c>
-      <c r="I231" t="n">
-        <v>1925</v>
       </c>
     </row>
     <row r="232">
@@ -9010,16 +9476,18 @@
       <c r="F232" t="n">
         <v>1</v>
       </c>
-      <c r="G232" t="n">
-        <v>1</v>
-      </c>
-      <c r="H232" t="inlineStr">
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="n">
+        <v>3301</v>
+      </c>
+      <c r="K232" t="inlineStr">
         <is>
           <t>FCSB</t>
         </is>
-      </c>
-      <c r="I232" t="n">
-        <v>3301</v>
       </c>
     </row>
     <row r="233">
@@ -9047,16 +9515,18 @@
       <c r="F233" t="n">
         <v>1</v>
       </c>
-      <c r="G233" t="n">
-        <v>1</v>
-      </c>
-      <c r="H233" t="inlineStr">
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="n">
+        <v>2351</v>
+      </c>
+      <c r="K233" t="inlineStr">
         <is>
           <t>Rangers</t>
         </is>
-      </c>
-      <c r="I233" t="n">
-        <v>2351</v>
       </c>
     </row>
     <row r="234">
@@ -9084,16 +9554,18 @@
       <c r="F234" t="n">
         <v>2</v>
       </c>
-      <c r="G234" t="n">
-        <v>1</v>
-      </c>
-      <c r="H234" t="inlineStr">
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="n">
+        <v>3052</v>
+      </c>
+      <c r="K234" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
-      </c>
-      <c r="I234" t="n">
-        <v>3052</v>
       </c>
     </row>
     <row r="235">
@@ -9121,16 +9593,18 @@
       <c r="F235" t="n">
         <v>2</v>
       </c>
-      <c r="G235" t="n">
-        <v>1</v>
-      </c>
-      <c r="H235" t="inlineStr">
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="n">
+        <v>2955</v>
+      </c>
+      <c r="K235" t="inlineStr">
         <is>
           <t>FC Twente</t>
         </is>
-      </c>
-      <c r="I235" t="n">
-        <v>2955</v>
       </c>
     </row>
     <row r="236">
@@ -9158,16 +9632,18 @@
       <c r="F236" t="n">
         <v>3</v>
       </c>
-      <c r="G236" t="n">
-        <v>1</v>
-      </c>
-      <c r="H236" t="inlineStr">
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="n">
+        <v>4860</v>
+      </c>
+      <c r="K236" t="inlineStr">
         <is>
           <t>Royale Union Saint-Gilloise</t>
         </is>
-      </c>
-      <c r="I236" t="n">
-        <v>4860</v>
       </c>
     </row>
     <row r="237">
@@ -9195,16 +9671,18 @@
       <c r="F237" t="n">
         <v>2</v>
       </c>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
-      <c r="H237" t="inlineStr">
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="n">
+        <v>3398</v>
+      </c>
+      <c r="K237" t="inlineStr">
         <is>
           <t>APOEL Nicosia</t>
         </is>
-      </c>
-      <c r="I237" t="n">
-        <v>3398</v>
       </c>
     </row>
     <row r="238">
@@ -9232,16 +9710,18 @@
       <c r="F238" t="n">
         <v>0</v>
       </c>
-      <c r="G238" t="n">
-        <v>1</v>
-      </c>
-      <c r="H238" t="inlineStr">
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="n">
+        <v>656</v>
+      </c>
+      <c r="K238" t="inlineStr">
         <is>
           <t>Bodø/Glimt</t>
         </is>
-      </c>
-      <c r="I238" t="n">
-        <v>656</v>
       </c>
     </row>
     <row r="239">
@@ -9269,16 +9749,18 @@
       <c r="F239" t="n">
         <v>0</v>
       </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
-      <c r="H239" t="inlineStr">
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K239" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I239" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="240">
@@ -9306,16 +9788,18 @@
       <c r="F240" t="n">
         <v>4</v>
       </c>
-      <c r="G240" t="n">
-        <v>1</v>
-      </c>
-      <c r="H240" t="inlineStr">
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="n">
+        <v>7691</v>
+      </c>
+      <c r="K240" t="inlineStr">
         <is>
           <t>Jagiellonia Białystok</t>
         </is>
-      </c>
-      <c r="I240" t="n">
-        <v>7691</v>
       </c>
     </row>
     <row r="241">
@@ -9343,16 +9827,18 @@
       <c r="F241" t="n">
         <v>3</v>
       </c>
-      <c r="G241" t="n">
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
         <v>3</v>
       </c>
-      <c r="H241" t="inlineStr">
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K241" t="inlineStr">
         <is>
           <t>Red Bull Salzburg</t>
         </is>
-      </c>
-      <c r="I241" t="n">
-        <v>2046</v>
       </c>
     </row>
     <row r="242">
@@ -9380,16 +9866,18 @@
       <c r="F242" t="n">
         <v>4</v>
       </c>
-      <c r="G242" t="n">
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
         <v>2</v>
       </c>
-      <c r="H242" t="inlineStr">
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>259121</v>
+      </c>
+      <c r="K242" t="inlineStr">
         <is>
           <t>FC Struga Trim &amp; Lum</t>
         </is>
-      </c>
-      <c r="I242" t="n">
-        <v>259121</v>
       </c>
     </row>
     <row r="243">
@@ -9417,16 +9905,18 @@
       <c r="F243" t="n">
         <v>2</v>
       </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" t="inlineStr">
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="n">
+        <v>7605</v>
+      </c>
+      <c r="K243" t="inlineStr">
         <is>
           <t>Differdange FC 03</t>
         </is>
-      </c>
-      <c r="I243" t="n">
-        <v>7605</v>
       </c>
     </row>
     <row r="244">
@@ -9454,16 +9944,18 @@
       <c r="F244" t="n">
         <v>3</v>
       </c>
-      <c r="G244" t="n">
-        <v>1</v>
-      </c>
-      <c r="H244" t="inlineStr">
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="n">
+        <v>37297</v>
+      </c>
+      <c r="K244" t="inlineStr">
         <is>
           <t>Dinamo Batumi</t>
         </is>
-      </c>
-      <c r="I244" t="n">
-        <v>37297</v>
       </c>
     </row>
     <row r="245">
@@ -9491,16 +9983,18 @@
       <c r="F245" t="n">
         <v>0</v>
       </c>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
-      <c r="H245" t="inlineStr">
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="n">
+        <v>5214</v>
+      </c>
+      <c r="K245" t="inlineStr">
         <is>
           <t>Pyunik Yerevan</t>
         </is>
-      </c>
-      <c r="I245" t="n">
-        <v>5214</v>
       </c>
     </row>
     <row r="246">
@@ -9528,16 +10022,18 @@
       <c r="F246" t="n">
         <v>1</v>
       </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" t="inlineStr">
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="n">
+        <v>264619</v>
+      </c>
+      <c r="K246" t="inlineStr">
         <is>
           <t>KF Egnatia</t>
         </is>
-      </c>
-      <c r="I246" t="n">
-        <v>264619</v>
       </c>
     </row>
     <row r="247">
@@ -9563,18 +10059,24 @@
         </is>
       </c>
       <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
+        <v>5</v>
+      </c>
+      <c r="H247" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" t="n">
         <v>6</v>
       </c>
-      <c r="G247" t="n">
-        <v>8</v>
-      </c>
-      <c r="H247" t="inlineStr">
+      <c r="J247" t="n">
+        <v>37949</v>
+      </c>
+      <c r="K247" t="inlineStr">
         <is>
           <t>UE Santa Coloma</t>
         </is>
-      </c>
-      <c r="I247" t="n">
-        <v>37949</v>
       </c>
     </row>
     <row r="248">
@@ -9600,18 +10102,24 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G248" t="n">
         <v>5</v>
       </c>
-      <c r="H248" t="inlineStr">
+      <c r="H248" t="n">
+        <v>1</v>
+      </c>
+      <c r="I248" t="n">
+        <v>4</v>
+      </c>
+      <c r="J248" t="n">
+        <v>33583</v>
+      </c>
+      <c r="K248" t="inlineStr">
         <is>
           <t>Ħamrun Spartans FC</t>
         </is>
-      </c>
-      <c r="I248" t="n">
-        <v>33583</v>
       </c>
     </row>
     <row r="249">
@@ -9639,16 +10147,18 @@
       <c r="F249" t="n">
         <v>0</v>
       </c>
-      <c r="G249" t="n">
-        <v>1</v>
-      </c>
-      <c r="H249" t="inlineStr">
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="n">
+        <v>3361</v>
+      </c>
+      <c r="K249" t="inlineStr">
         <is>
           <t>Dinamo Minsk</t>
         </is>
-      </c>
-      <c r="I249" t="n">
-        <v>3361</v>
       </c>
     </row>
     <row r="250">
@@ -9676,16 +10186,18 @@
       <c r="F250" t="n">
         <v>1</v>
       </c>
-      <c r="G250" t="n">
-        <v>1</v>
-      </c>
-      <c r="H250" t="inlineStr">
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="n">
+        <v>192763</v>
+      </c>
+      <c r="K250" t="inlineStr">
         <is>
           <t>FK Panevėžys</t>
         </is>
-      </c>
-      <c r="I250" t="n">
-        <v>192763</v>
       </c>
     </row>
     <row r="251">
@@ -9713,16 +10225,18 @@
       <c r="F251" t="n">
         <v>2</v>
       </c>
-      <c r="G251" t="n">
-        <v>1</v>
-      </c>
-      <c r="H251" t="inlineStr">
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="n">
+        <v>3346</v>
+      </c>
+      <c r="K251" t="inlineStr">
         <is>
           <t>Flora Tallinn</t>
         </is>
-      </c>
-      <c r="I251" t="n">
-        <v>3346</v>
       </c>
     </row>
     <row r="252">
@@ -9750,16 +10264,18 @@
       <c r="F252" t="n">
         <v>4</v>
       </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-      <c r="H252" t="inlineStr">
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="n">
+        <v>36261</v>
+      </c>
+      <c r="K252" t="inlineStr">
         <is>
           <t>SS Virtus</t>
         </is>
-      </c>
-      <c r="I252" t="n">
-        <v>36261</v>
       </c>
     </row>
     <row r="253">
@@ -9787,16 +10303,18 @@
       <c r="F253" t="n">
         <v>1</v>
       </c>
-      <c r="G253" t="n">
-        <v>1</v>
-      </c>
-      <c r="H253" t="inlineStr">
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="n">
+        <v>4921</v>
+      </c>
+      <c r="K253" t="inlineStr">
         <is>
           <t>The New Saints</t>
         </is>
-      </c>
-      <c r="I253" t="n">
-        <v>4921</v>
       </c>
     </row>
     <row r="254">
@@ -9824,16 +10342,18 @@
       <c r="F254" t="n">
         <v>2</v>
       </c>
-      <c r="G254" t="n">
-        <v>1</v>
-      </c>
-      <c r="H254" t="inlineStr">
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="n">
+        <v>1908</v>
+      </c>
+      <c r="K254" t="inlineStr">
         <is>
           <t>Víkingur Reykjavík</t>
         </is>
-      </c>
-      <c r="I254" t="n">
-        <v>1908</v>
       </c>
     </row>
     <row r="255">
@@ -9861,16 +10381,18 @@
       <c r="F255" t="n">
         <v>1</v>
       </c>
-      <c r="G255" t="n">
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="n">
         <v>2</v>
       </c>
-      <c r="H255" t="inlineStr">
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="n">
+        <v>2404</v>
+      </c>
+      <c r="K255" t="inlineStr">
         <is>
           <t>ŠK Slovan Bratislava</t>
         </is>
-      </c>
-      <c r="I255" t="n">
-        <v>2404</v>
       </c>
     </row>
     <row r="256">
@@ -9898,16 +10420,18 @@
       <c r="F256" t="n">
         <v>1</v>
       </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-      <c r="H256" t="inlineStr">
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="n">
+        <v>5366</v>
+      </c>
+      <c r="K256" t="inlineStr">
         <is>
           <t>FC Ordabasy</t>
         </is>
-      </c>
-      <c r="I256" t="n">
-        <v>5366</v>
       </c>
     </row>
     <row r="257">
@@ -9935,16 +10459,18 @@
       <c r="F257" t="n">
         <v>0</v>
       </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-      <c r="H257" t="inlineStr">
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="n">
+        <v>5194</v>
+      </c>
+      <c r="K257" t="inlineStr">
         <is>
           <t>Klaksvíkar Ítróttarfelag</t>
         </is>
-      </c>
-      <c r="I257" t="n">
-        <v>5194</v>
       </c>
     </row>
     <row r="258">
@@ -9972,16 +10498,18 @@
       <c r="F258" t="n">
         <v>1</v>
       </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-      <c r="H258" t="inlineStr">
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="n">
+        <v>43840</v>
+      </c>
+      <c r="K258" t="inlineStr">
         <is>
           <t>Ludogorets</t>
         </is>
-      </c>
-      <c r="I258" t="n">
-        <v>43840</v>
       </c>
     </row>
     <row r="259">
@@ -10007,18 +10535,24 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G259" t="n">
-        <v>5</v>
-      </c>
-      <c r="H259" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" t="n">
+        <v>4</v>
+      </c>
+      <c r="J259" t="n">
+        <v>5235</v>
+      </c>
+      <c r="K259" t="inlineStr">
         <is>
           <t>FK Borac Banja Luka</t>
         </is>
-      </c>
-      <c r="I259" t="n">
-        <v>5235</v>
       </c>
     </row>
     <row r="260">
@@ -10046,16 +10580,18 @@
       <c r="F260" t="n">
         <v>0</v>
       </c>
-      <c r="G260" t="n">
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="n">
         <v>4</v>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="n">
+        <v>68718</v>
+      </c>
+      <c r="K260" t="inlineStr">
         <is>
           <t>RFS</t>
         </is>
-      </c>
-      <c r="I260" t="n">
-        <v>68718</v>
       </c>
     </row>
     <row r="261">
@@ -10083,16 +10619,18 @@
       <c r="F261" t="n">
         <v>4</v>
       </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-      <c r="H261" t="inlineStr">
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="n">
+        <v>68718</v>
+      </c>
+      <c r="K261" t="inlineStr">
         <is>
           <t>RFS</t>
         </is>
-      </c>
-      <c r="I261" t="n">
-        <v>68718</v>
       </c>
     </row>
     <row r="262">
@@ -10120,16 +10658,18 @@
       <c r="F262" t="n">
         <v>0</v>
       </c>
-      <c r="G262" t="n">
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="n">
         <v>4</v>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="n">
+        <v>7691</v>
+      </c>
+      <c r="K262" t="inlineStr">
         <is>
           <t>Jagiellonia Białystok</t>
         </is>
-      </c>
-      <c r="I262" t="n">
-        <v>7691</v>
       </c>
     </row>
     <row r="263">
@@ -10157,16 +10697,18 @@
       <c r="F263" t="n">
         <v>0</v>
       </c>
-      <c r="G263" t="n">
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="n">
         <v>2</v>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="n">
+        <v>5962</v>
+      </c>
+      <c r="K263" t="inlineStr">
         <is>
           <t>Qarabağ FK</t>
         </is>
-      </c>
-      <c r="I263" t="n">
-        <v>5962</v>
       </c>
     </row>
     <row r="264">
@@ -10194,16 +10736,18 @@
       <c r="F264" t="n">
         <v>1</v>
       </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" t="inlineStr">
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="n">
+        <v>167232</v>
+      </c>
+      <c r="K264" t="inlineStr">
         <is>
           <t>FC Petrocub Hîncesti</t>
         </is>
-      </c>
-      <c r="I264" t="n">
-        <v>167232</v>
       </c>
     </row>
     <row r="265">
@@ -10231,16 +10775,18 @@
       <c r="F265" t="n">
         <v>4</v>
       </c>
-      <c r="G265" t="n">
-        <v>1</v>
-      </c>
-      <c r="H265" t="inlineStr">
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="n">
+        <v>5194</v>
+      </c>
+      <c r="K265" t="inlineStr">
         <is>
           <t>Klaksvíkar Ítróttarfelag</t>
         </is>
-      </c>
-      <c r="I265" t="n">
-        <v>5194</v>
       </c>
     </row>
     <row r="266">
@@ -10268,16 +10814,18 @@
       <c r="F266" t="n">
         <v>1</v>
       </c>
-      <c r="G266" t="n">
-        <v>1</v>
-      </c>
-      <c r="H266" t="inlineStr">
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="n">
+        <v>5198</v>
+      </c>
+      <c r="K266" t="inlineStr">
         <is>
           <t>Maccabi Tel Aviv</t>
         </is>
-      </c>
-      <c r="I266" t="n">
-        <v>5198</v>
       </c>
     </row>
     <row r="267">
@@ -10305,16 +10853,18 @@
       <c r="F267" t="n">
         <v>0</v>
       </c>
-      <c r="G267" t="n">
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="n">
         <v>3</v>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="n">
+        <v>1289</v>
+      </c>
+      <c r="K267" t="inlineStr">
         <is>
           <t>FC Midtjylland</t>
         </is>
-      </c>
-      <c r="I267" t="n">
-        <v>1289</v>
       </c>
     </row>
     <row r="268">
@@ -10342,16 +10892,18 @@
       <c r="F268" t="n">
         <v>5</v>
       </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" t="inlineStr">
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="n">
+        <v>4921</v>
+      </c>
+      <c r="K268" t="inlineStr">
         <is>
           <t>The New Saints</t>
         </is>
-      </c>
-      <c r="I268" t="n">
-        <v>4921</v>
       </c>
     </row>
     <row r="269">
@@ -10379,16 +10931,18 @@
       <c r="F269" t="n">
         <v>6</v>
       </c>
-      <c r="G269" t="n">
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="n">
         <v>2</v>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="n">
+        <v>5152</v>
+      </c>
+      <c r="K269" t="inlineStr">
         <is>
           <t>FK Partizan</t>
         </is>
-      </c>
-      <c r="I269" t="n">
-        <v>5152</v>
       </c>
     </row>
     <row r="270">
@@ -10416,16 +10970,18 @@
       <c r="F270" t="n">
         <v>3</v>
       </c>
-      <c r="G270" t="n">
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="n">
         <v>4</v>
       </c>
-      <c r="H270" t="inlineStr">
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="n">
+        <v>3052</v>
+      </c>
+      <c r="K270" t="inlineStr">
         <is>
           <t>Fenerbahçe</t>
         </is>
-      </c>
-      <c r="I270" t="n">
-        <v>3052</v>
       </c>
     </row>
     <row r="271">
@@ -10453,16 +11009,18 @@
       <c r="F271" t="n">
         <v>0</v>
       </c>
-      <c r="G271" t="n">
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="n">
         <v>2</v>
       </c>
-      <c r="H271" t="inlineStr">
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="n">
+        <v>2218</v>
+      </c>
+      <c r="K271" t="inlineStr">
         <is>
           <t>AC Sparta Praha</t>
         </is>
-      </c>
-      <c r="I271" t="n">
-        <v>2218</v>
       </c>
     </row>
     <row r="272">
@@ -10490,16 +11048,18 @@
       <c r="F272" t="n">
         <v>3</v>
       </c>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
-      <c r="H272" t="inlineStr">
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="n">
+        <v>2242</v>
+      </c>
+      <c r="K272" t="inlineStr">
         <is>
           <t>HJK</t>
         </is>
-      </c>
-      <c r="I272" t="n">
-        <v>2242</v>
       </c>
     </row>
     <row r="273">
@@ -10527,16 +11087,18 @@
       <c r="F273" t="n">
         <v>0</v>
       </c>
-      <c r="G273" t="n">
-        <v>1</v>
-      </c>
-      <c r="H273" t="inlineStr">
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="n">
+        <v>126304</v>
+      </c>
+      <c r="K273" t="inlineStr">
         <is>
           <t>Lincoln Red Imps</t>
         </is>
-      </c>
-      <c r="I273" t="n">
-        <v>126304</v>
       </c>
     </row>
     <row r="274">
@@ -10564,16 +11126,18 @@
       <c r="F274" t="n">
         <v>1</v>
       </c>
-      <c r="G274" t="n">
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="n">
         <v>2</v>
       </c>
-      <c r="H274" t="inlineStr">
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="n">
+        <v>230417</v>
+      </c>
+      <c r="K274" t="inlineStr">
         <is>
           <t>KF Ballkani</t>
         </is>
-      </c>
-      <c r="I274" t="n">
-        <v>230417</v>
       </c>
     </row>
     <row r="275">
@@ -10601,16 +11165,18 @@
       <c r="F275" t="n">
         <v>3</v>
       </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-      <c r="H275" t="inlineStr">
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="n">
+        <v>0</v>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="n">
+        <v>6226</v>
+      </c>
+      <c r="K275" t="inlineStr">
         <is>
           <t>FK Dečić Tuzi</t>
         </is>
-      </c>
-      <c r="I275" t="n">
-        <v>6226</v>
       </c>
     </row>
     <row r="276">
@@ -10638,16 +11204,18 @@
       <c r="F276" t="n">
         <v>0</v>
       </c>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
-      <c r="H276" t="inlineStr">
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="n">
+        <v>3177</v>
+      </c>
+      <c r="K276" t="inlineStr">
         <is>
           <t>Shamrock Rovers</t>
         </is>
-      </c>
-      <c r="I276" t="n">
-        <v>3177</v>
       </c>
     </row>
     <row r="277">
@@ -10675,16 +11243,18 @@
       <c r="F277" t="n">
         <v>1</v>
       </c>
-      <c r="G277" t="n">
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="n">
         <v>7</v>
       </c>
-      <c r="H277" t="inlineStr">
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="n">
+        <v>3301</v>
+      </c>
+      <c r="K277" t="inlineStr">
         <is>
           <t>FCSB</t>
         </is>
-      </c>
-      <c r="I277" t="n">
-        <v>3301</v>
       </c>
     </row>
     <row r="278">
@@ -10712,16 +11282,18 @@
       <c r="F278" t="n">
         <v>0</v>
       </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-      <c r="H278" t="inlineStr">
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="n">
+        <v>167232</v>
+      </c>
+      <c r="K278" t="inlineStr">
         <is>
           <t>FC Petrocub Hîncesti</t>
         </is>
-      </c>
-      <c r="I278" t="n">
-        <v>167232</v>
       </c>
     </row>
     <row r="279">
@@ -10749,16 +11321,18 @@
       <c r="F279" t="n">
         <v>0</v>
       </c>
-      <c r="G279" t="n">
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="n">
         <v>5</v>
       </c>
-      <c r="H279" t="inlineStr">
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="n">
+        <v>2413</v>
+      </c>
+      <c r="K279" t="inlineStr">
         <is>
           <t>NK Celje</t>
         </is>
-      </c>
-      <c r="I279" t="n">
-        <v>2413</v>
       </c>
     </row>
     <row r="280">
@@ -10786,16 +11360,18 @@
       <c r="F280" t="n">
         <v>3</v>
       </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-      <c r="H280" t="inlineStr">
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="n">
+        <v>5184</v>
+      </c>
+      <c r="K280" t="inlineStr">
         <is>
           <t>Larne FC</t>
         </is>
-      </c>
-      <c r="I280" t="n">
-        <v>5184</v>
       </c>
     </row>
   </sheetData>
